--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484231_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484231_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. NOGUER SANTAELLA</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.9343</v>
+        <v>-0.6635</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9728</v>
+        <v>1.6974</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.9071</v>
+        <v>-2.3609</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0181</v>
+        <v>3.2543</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3466</v>
+        <v>-1.3988</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3648</v>
+        <v>4.6532</v>
       </c>
       <c r="J2" t="n">
-        <v>1.7596</v>
+        <v>6.2555</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7191</v>
+        <v>0.6574</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0405</v>
+        <v>5.5981</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7777</v>
+        <v>-3.0012</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3725</v>
+        <v>-2.0563</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4052</v>
+        <v>-0.9449</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7814</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.1953</v>
+        <v>-4.1022</v>
       </c>
       <c r="R2" t="n">
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7891</v>
+        <v>-0.4932</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5915</v>
+        <v>-0.4559</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1976</v>
+        <v>-0.0373</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9085</v>
+        <v>-0.2992</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.9085</v>
+        <v>-0.2992</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>R. NOGUER SANTAELLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.1151</v>
+        <v>-0.7533</v>
       </c>
       <c r="E3" t="n">
-        <v>1.273</v>
+        <v>1.2355</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.3882</v>
+        <v>-1.9888</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2543</v>
+        <v>-0.0181</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3988</v>
+        <v>0.3466</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6532</v>
+        <v>-0.3648</v>
       </c>
       <c r="J3" t="n">
-        <v>6.2555</v>
+        <v>1.7596</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6574</v>
+        <v>1.7191</v>
       </c>
       <c r="L3" t="n">
-        <v>5.5981</v>
+        <v>0.0405</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0012</v>
+        <v>-1.7777</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0563</v>
+        <v>-1.3725</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9449</v>
+        <v>-0.4052</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.1255</v>
+        <v>0.7814</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.1022</v>
+        <v>-0.1953</v>
       </c>
       <c r="R3" t="n">
         <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9448</v>
+        <v>-0.608</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8803</v>
+        <v>-0.3287</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0645</v>
+        <v>-0.2793</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2992</v>
+        <v>-0.9085</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2992</v>
+        <v>-0.9085</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.3437</v>
+        <v>-2.8511</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.0768</v>
+        <v>-2.4208</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2669</v>
+        <v>-0.4303</v>
       </c>
       <c r="G4" t="n">
         <v>-2.77</v>
@@ -766,13 +766,13 @@
         <v>0.9767</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0589</v>
+        <v>-0.4485</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0689</v>
+        <v>-0.2751</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.01</v>
+        <v>-0.1734</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6093</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>A. CANO CANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.1273</v>
+        <v>-3.101</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3146</v>
+        <v>-3.2608</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8126</v>
+        <v>0.1597</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6683</v>
+        <v>-3.6934</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.7491</v>
+        <v>-0.8079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08069999999999999</v>
+        <v>-2.8855</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-2.595</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7112000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6208</v>
+        <v>-2.6155</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5779</v>
+        <v>-1.0984</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0379</v>
+        <v>-0.8283</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5401</v>
+        <v>-0.27</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6543</v>
+        <v>-1.322</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0522</v>
+        <v>-0.6657</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6021</v>
+        <v>-0.6563</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6093</v>
+        <v>1.3283</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6093</v>
+        <v>1.3283</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CANO CANO</t>
+          <t>F. DIAZ CABANAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.2372</v>
+        <v>-3.1659</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.2608</v>
+        <v>-3.4719</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0236</v>
+        <v>0.306</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.6934</v>
+        <v>-3.4207</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8079</v>
+        <v>-1.5733</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.8855</v>
+        <v>-1.8474</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.595</v>
+        <v>-3.0013</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>-1.0195</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.6155</v>
+        <v>-1.9818</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0984</v>
+        <v>-0.4194</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8283</v>
+        <v>-0.5538</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.27</v>
+        <v>0.1344</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4582</v>
+        <v>-0.8419</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6657</v>
+        <v>-0.7125</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7924</v>
+        <v>-0.1294</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3283</v>
+        <v>1.0968</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>1.3283</v>
+        <v>-0.1219</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. DIAZ CABANAS</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.2748</v>
+        <v>-3.5123</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.4719</v>
+        <v>-1.618</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1971</v>
+        <v>-1.8943</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.4207</v>
+        <v>-1.6683</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5733</v>
+        <v>-1.7491</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8474</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-3.0013</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0195</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9818</v>
+        <v>0.6208</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4194</v>
+        <v>-1.5779</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5538</v>
+        <v>-1.0379</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1344</v>
+        <v>-0.5401</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9508</v>
+        <v>-1.0393</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7125</v>
+        <v>-0.3555</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2383</v>
+        <v>-0.6838</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0968</v>
+        <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1219</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.1805</v>
+        <v>-3.5171</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9673</v>
+        <v>-1.6035</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2132</v>
+        <v>-1.9136</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1355</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-2.0563</v>
+        <v>-1.3929</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.271</v>
+        <v>-0.9071</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7853</v>
+        <v>-0.4858</v>
       </c>
       <c r="V8" t="n">
         <v>0.9414</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4062</v>
+        <v>-4.3692</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0113</v>
+        <v>-1.6474</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3949</v>
+        <v>-2.7217</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3301</v>
@@ -1156,13 +1156,13 @@
         <v>0.7814</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1849</v>
+        <v>-0.1479</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0013</v>
+        <v>-0.6375</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8164</v>
+        <v>0.4896</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6726</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1467</v>
+        <v>-5.2901</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7926</v>
+        <v>-2.7727</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3541</v>
+        <v>-2.5175</v>
       </c>
       <c r="G10" t="n">
         <v>-2.253</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6344</v>
+        <v>-0.7779</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5831</v>
+        <v>-0.5632</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0513</v>
+        <v>-0.2148</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6732</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5342</v>
+        <v>-5.5397</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5999</v>
+        <v>-3.7416</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9343</v>
+        <v>-1.7981</v>
       </c>
       <c r="G11" t="n">
         <v>-4.8086</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1597</v>
+        <v>0.1541</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3385</v>
+        <v>0.1968</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1789</v>
+        <v>-0.0427</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2992</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9314</v>
+        <v>-5.863</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2169</v>
+        <v>-2.2575</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.7144</v>
+        <v>-3.6055</v>
       </c>
       <c r="G12" t="n">
         <v>-3.8754</v>
@@ -1390,13 +1390,13 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5931</v>
+        <v>-0.5248</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.22</v>
+        <v>-0.2606</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3732</v>
+        <v>-0.2642</v>
       </c>
       <c r="V12" t="n">
         <v>0.0999</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-39.23140000000001</v>
+        <v>-38.6262</v>
       </c>
       <c r="E13" t="n">
-        <v>-20.4663</v>
+        <v>-19.8613</v>
       </c>
       <c r="F13" t="n">
         <v>-18.765</v>
@@ -1438,7 +1438,7 @@
         <v>-18.6713</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.0475</v>
+        <v>-4.047499999999999</v>
       </c>
       <c r="J13" t="n">
         <v>-2.8697</v>
@@ -1468,13 +1468,13 @@
         <v>9.767000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.0473</v>
+        <v>-7.442299999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.5702</v>
+        <v>-4.965000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.4772</v>
+        <v>-2.4774</v>
       </c>
       <c r="V13" t="n">
         <v>-2.6049</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5289</v>
+        <v>7.7169</v>
       </c>
       <c r="E14" t="n">
         <v>4.895</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6339</v>
+        <v>2.8219</v>
       </c>
       <c r="G14" t="n">
         <v>4.7456</v>
@@ -1546,13 +1546,13 @@
         <v>1.3674</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8066</v>
+        <v>0.9946</v>
       </c>
       <c r="T14" t="n">
         <v>0.1294</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6772</v>
+        <v>0.8652</v>
       </c>
       <c r="V14" t="n">
         <v>0.6093</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7221</v>
+        <v>6.2131</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9144</v>
+        <v>4.5749</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8077</v>
+        <v>1.6382</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7201</v>
+        <v>2.9421</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7475</v>
+        <v>1.8491</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0274</v>
+        <v>1.093</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0802</v>
+        <v>2.8267</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2975</v>
+        <v>2.273</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7827</v>
+        <v>0.5537</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3601</v>
+        <v>0.1154</v>
       </c>
       <c r="N15" t="n">
-        <v>0.45</v>
+        <v>-0.4239</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8101</v>
+        <v>0.5393</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6113</v>
+        <v>0.271</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2943</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9055</v>
+        <v>0.3507</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6093</v>
+        <v>1.8279</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1052</v>
+        <v>1.8279</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.701</v>
+        <v>6.1122</v>
       </c>
       <c r="E16" t="n">
-        <v>4.1704</v>
+        <v>5.1166</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5306</v>
+        <v>0.9956</v>
       </c>
       <c r="G16" t="n">
-        <v>2.9421</v>
+        <v>3.7201</v>
       </c>
       <c r="H16" t="n">
-        <v>1.8491</v>
+        <v>3.7475</v>
       </c>
       <c r="I16" t="n">
-        <v>1.093</v>
+        <v>-0.0274</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8267</v>
+        <v>4.0802</v>
       </c>
       <c r="K16" t="n">
-        <v>2.273</v>
+        <v>3.2975</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5537</v>
+        <v>0.7827</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1154</v>
+        <v>-0.3601</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4239</v>
+        <v>0.45</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5393</v>
+        <v>-0.8101</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.241</v>
+        <v>1.0014</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4842</v>
+        <v>-0.092</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2431</v>
+        <v>1.0935</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8279</v>
+        <v>0.6093</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8279</v>
+        <v>2.1052</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.4792</v>
+        <v>5.2848</v>
       </c>
       <c r="E17" t="n">
-        <v>4.9327</v>
+        <v>4.6293</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5465</v>
+        <v>0.6554</v>
       </c>
       <c r="G17" t="n">
         <v>4.9644</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2255</v>
+        <v>1.0311</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6219</v>
+        <v>0.3186</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6036</v>
+        <v>0.7125</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8828</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.8033</v>
+        <v>5.0627</v>
       </c>
       <c r="E18" t="n">
-        <v>1.524</v>
+        <v>1.3218</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2793</v>
+        <v>3.7409</v>
       </c>
       <c r="G18" t="n">
         <v>1.5655</v>
@@ -1858,13 +1858,13 @@
         <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7104</v>
+        <v>0.9698</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5009</v>
+        <v>0.2987</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2095</v>
+        <v>0.6712</v>
       </c>
       <c r="V18" t="n">
         <v>1.5507</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.4787</v>
+        <v>4.3684</v>
       </c>
       <c r="E19" t="n">
         <v>1.744</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7347</v>
+        <v>2.6244</v>
       </c>
       <c r="G19" t="n">
         <v>2.9064</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7444</v>
+        <v>0.6341</v>
       </c>
       <c r="T19" t="n">
         <v>0.3715</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3729</v>
+        <v>0.2626</v>
       </c>
       <c r="V19" t="n">
         <v>1.2186</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>3.6475</v>
+        <v>2.6647</v>
       </c>
       <c r="E20" t="n">
-        <v>2.3125</v>
+        <v>0.9767</v>
       </c>
       <c r="F20" t="n">
-        <v>1.335</v>
+        <v>1.688</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1058</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8885</v>
+        <v>1.7227</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7827</v>
+        <v>-1.1194</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1861</v>
+        <v>0.8136</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6984</v>
+        <v>1.3929</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5122</v>
+        <v>-0.5794</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0803</v>
+        <v>-0.2103</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1901</v>
+        <v>0.3298</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2704</v>
+        <v>-0.5401</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5296</v>
+        <v>0.694</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8491</v>
+        <v>0.1631</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6806</v>
+        <v>0.5309</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8221</v>
+        <v>2.4069</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2689</v>
+        <v>1.0991</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5532</v>
+        <v>1.3078</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.1058</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7227</v>
+        <v>0.8885</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1194</v>
+        <v>-0.7827</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8136</v>
+        <v>0.1861</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3929</v>
+        <v>0.6984</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5794</v>
+        <v>-0.5122</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2103</v>
+        <v>-0.0803</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3298</v>
+        <v>0.1901</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5401</v>
+        <v>-0.2704</v>
       </c>
       <c r="P21" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1486</v>
+        <v>1.289</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5447</v>
+        <v>0.6357</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3961</v>
+        <v>0.6533</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.0466</v>
+        <v>1.2319</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9411</v>
+        <v>-1.1446</v>
       </c>
       <c r="F22" t="n">
-        <v>2.9878</v>
+        <v>2.3765</v>
       </c>
       <c r="G22" t="n">
-        <v>0.781</v>
+        <v>2.492</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5249</v>
+        <v>2.8698</v>
       </c>
       <c r="I22" t="n">
-        <v>0.256</v>
+        <v>-0.3778</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2227</v>
+        <v>2.1074</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3441</v>
+        <v>2.6196</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>-0.5122</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0037</v>
+        <v>0.3846</v>
       </c>
       <c r="N22" t="n">
-        <v>0.869</v>
+        <v>0.2502</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1346</v>
+        <v>0.1344</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.9534</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q22" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>2.606</v>
+        <v>0.498</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5986</v>
+        <v>-0.3218</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0074</v>
+        <v>0.8198</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5837</v>
+        <v>-0.0152</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.549</v>
+        <v>-2.6489</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1327</v>
+        <v>2.6337</v>
       </c>
       <c r="G23" t="n">
-        <v>2.492</v>
+        <v>0.781</v>
       </c>
       <c r="H23" t="n">
-        <v>2.8698</v>
+        <v>0.5249</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3778</v>
+        <v>0.256</v>
       </c>
       <c r="J23" t="n">
-        <v>2.1074</v>
+        <v>-0.2227</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6196</v>
+        <v>-0.3441</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.5122</v>
+        <v>0.1214</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3846</v>
+        <v>1.0037</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2502</v>
+        <v>0.869</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1344</v>
+        <v>0.1346</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.7581</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.9301</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1503</v>
+        <v>1.5442</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.8908</v>
       </c>
       <c r="U23" t="n">
-        <v>0.576</v>
+        <v>0.6533</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.5818</v>
+        <v>-0.4668</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5067</v>
+        <v>-1.7989</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9249000000000001</v>
+        <v>1.3321</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1073</v>
@@ -2326,13 +2326,13 @@
         <v>1.1721</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6466</v>
+        <v>0.4684</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5447</v>
+        <v>0.1631</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1018</v>
+        <v>0.3053</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>39.2313</v>
+        <v>40.57960000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>18.7651</v>
+        <v>18.765</v>
       </c>
       <c r="F25" t="n">
-        <v>20.4663</v>
+        <v>21.8145</v>
       </c>
       <c r="G25" t="n">
         <v>22.7189</v>
@@ -2404,19 +2404,19 @@
         <v>15.6275</v>
       </c>
       <c r="S25" t="n">
-        <v>8.047300000000002</v>
+        <v>9.3956</v>
       </c>
       <c r="T25" t="n">
-        <v>2.4772</v>
+        <v>2.4774</v>
       </c>
       <c r="U25" t="n">
-        <v>5.5701</v>
+        <v>6.9183</v>
       </c>
       <c r="V25" t="n">
-        <v>2.6047</v>
+        <v>2.604699999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>6.2057</v>
+        <v>6.205699999999999</v>
       </c>
       <c r="X25" t="n">
         <v>-3.601</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484231_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484231_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2992</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.9085</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>1.3283</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1219</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.6093</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.3405</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6732</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.2992</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.3959</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.2059</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,11 +2039,16 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6647</v>
+        <v>2.4069</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9767</v>
+        <v>1.0991</v>
       </c>
       <c r="F20" t="n">
-        <v>1.688</v>
+        <v>1.3078</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.1058</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7227</v>
+        <v>0.8885</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1194</v>
+        <v>-0.7827</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8136</v>
+        <v>0.1861</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3929</v>
+        <v>0.6984</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5794</v>
+        <v>-0.5122</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2103</v>
+        <v>-0.0803</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3298</v>
+        <v>0.1901</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5401</v>
+        <v>-0.2704</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S20" t="n">
-        <v>0.694</v>
+        <v>1.289</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1631</v>
+        <v>0.6357</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5309</v>
+        <v>0.6533</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2143,72 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4069</v>
+        <v>1.8349</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0991</v>
+        <v>1.8349</v>
       </c>
       <c r="F21" t="n">
-        <v>1.3078</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1058</v>
+        <v>1.8349</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8885</v>
+        <v>1.2279</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7827</v>
+        <v>0.607</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1861</v>
+        <v>1.8349</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6984</v>
+        <v>1.2279</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5122</v>
+        <v>0.607</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0803</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1901</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2704</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.289</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6357</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6533</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -2187,11 +2288,16 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0152</v>
+        <v>0.8298</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6489</v>
+        <v>-0.8582</v>
       </c>
       <c r="F23" t="n">
-        <v>2.6337</v>
+        <v>1.688</v>
       </c>
       <c r="G23" t="n">
-        <v>0.781</v>
+        <v>-1.2316</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5249</v>
+        <v>0.4948</v>
       </c>
       <c r="I23" t="n">
-        <v>0.256</v>
+        <v>-1.7264</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2227</v>
+        <v>-1.0213</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3441</v>
+        <v>0.165</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1214</v>
+        <v>-1.1863</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0037</v>
+        <v>-0.2103</v>
       </c>
       <c r="N23" t="n">
-        <v>0.869</v>
+        <v>0.3298</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1346</v>
+        <v>-0.5401</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9767</v>
+        <v>1.3674</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5442</v>
+        <v>0.694</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8908</v>
+        <v>0.1631</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6533</v>
+        <v>0.5309</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4668</v>
+        <v>-0.0152</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7989</v>
+        <v>-2.6489</v>
       </c>
       <c r="F24" t="n">
-        <v>1.3321</v>
+        <v>2.6337</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1073</v>
+        <v>0.781</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4213</v>
+        <v>0.5249</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6859</v>
+        <v>0.256</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.962</v>
+        <v>-0.2227</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8161</v>
+        <v>-0.3441</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1459</v>
+        <v>0.1214</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1453</v>
+        <v>1.0037</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3948</v>
+        <v>0.869</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5401</v>
+        <v>0.1346</v>
       </c>
       <c r="P24" t="n">
-        <v>1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4684</v>
+        <v>1.5442</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1631</v>
+        <v>0.8908</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3053</v>
+        <v>0.6533</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,152 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>40.57960000000001</v>
+        <v>-0.4668</v>
       </c>
       <c r="E25" t="n">
+        <v>-1.7989</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.3321</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.1073</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.4213</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.6859</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.962</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.8161</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.1459</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.1453</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5401</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1631</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484231_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>40.5796</v>
+      </c>
+      <c r="E26" t="n">
         <v>18.765</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F26" t="n">
         <v>21.8145</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G26" t="n">
         <v>22.7189</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H26" t="n">
         <v>18.6712</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I26" t="n">
         <v>4.0477</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J26" t="n">
         <v>19.8491</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K26" t="n">
         <v>14.4474</v>
       </c>
-      <c r="L25" t="n">
-        <v>5.4017</v>
-      </c>
-      <c r="M25" t="n">
-        <v>2.8698</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="L26" t="n">
+        <v>5.401800000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2.869799999999999</v>
+      </c>
+      <c r="N26" t="n">
         <v>4.2238</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O26" t="n">
         <v>-1.3542</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P26" t="n">
         <v>5.8604</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q26" t="n">
         <v>-9.766999999999999</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R26" t="n">
         <v>15.6275</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S26" t="n">
         <v>9.3956</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T26" t="n">
         <v>2.4774</v>
       </c>
-      <c r="U25" t="n">
-        <v>6.9183</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="U26" t="n">
+        <v>6.918299999999999</v>
+      </c>
+      <c r="V26" t="n">
         <v>2.604699999999999</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W26" t="n">
         <v>6.205699999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X26" t="n">
         <v>-3.601</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
